--- a/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>PCAR</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35127400</v>
+      </c>
+      <c r="E8" s="3">
         <v>28819700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23522300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18728500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25599700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23495700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19456400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17032900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19115100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18997000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17123800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17050500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16355200</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>26894200</v>
+      </c>
+      <c r="E9" s="3">
         <v>23291000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19092400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15076400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20555100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18925300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15593400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13517300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15292800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15486900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13902000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>27975300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13523100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8233200</v>
+      </c>
+      <c r="E10" s="3">
         <v>5528700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4429900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3652100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5044600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4570400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3863000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3515600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3822300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3510100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3221800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-10924800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2832100</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,50 +875,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>410900</v>
+      </c>
+      <c r="E12" s="3">
         <v>341200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>324100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>273900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>326600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>306100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>264700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>247200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>239800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>215600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>251400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>279300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>288200</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -946,14 +962,17 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>600000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>10</v>
@@ -970,11 +989,11 @@
       <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="3">
         <v>833000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
@@ -988,51 +1007,57 @@
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>590700</v>
+      </c>
+      <c r="E15" s="3">
         <v>560800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>969400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1008000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>798200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>728000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>727500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>635200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>583700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>588500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>571700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>517400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>346600</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29280400</v>
+      </c>
+      <c r="E17" s="3">
         <v>24924800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21063200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16968500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>22393700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20618900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17162400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15789500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16672500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16862600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15297500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15296900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14875800</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5847000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3894900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2459100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1760000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3206000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2876800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2294000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1243400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2442600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2134400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1826300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1753600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1479400</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>371800</v>
+      </c>
+      <c r="E20" s="3">
         <v>170100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>88100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>90000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>133800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>135200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-20100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>42500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>20100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>35700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>33100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>27500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7142700</v>
+      </c>
+      <c r="E21" s="3">
         <v>4855200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3450500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2899000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4417100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4066100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3381400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2279000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3369800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3064800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2672700</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2180700</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>500600</v>
+      </c>
+      <c r="E22" s="3">
         <v>216300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>150900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>192100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>240600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>201800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>100600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>155500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>125600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>129500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>167000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>157800</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5718200</v>
+      </c>
+      <c r="E23" s="3">
         <v>3848700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2396300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1657900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3099200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2810200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2173300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1130400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2337100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2017600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1695000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1628900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1506900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1117400</v>
+      </c>
+      <c r="E24" s="3">
         <v>837100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>530800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>359500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>711300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>615100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>671500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>608700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>733100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>658800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>523700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>517300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>464600</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4600800</v>
+      </c>
+      <c r="E26" s="3">
         <v>3011600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1865500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1298400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2387900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2195100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1501800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>521700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1604000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1358800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1171300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1111600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1042300</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4600800</v>
+      </c>
+      <c r="E27" s="3">
         <v>3011600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1865500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1298400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2387900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2195100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1501800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>521700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1604000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1358800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1171300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1111600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1042300</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1546,11 +1606,11 @@
       <c r="H29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="3">
         <v>173400</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-371800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-170100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-88100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-90000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-133800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-135200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>20100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-42500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-20100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-35700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-33100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-27500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4600800</v>
+      </c>
+      <c r="E33" s="3">
         <v>3011600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1865500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1298400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2387900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2195100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1675200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>521700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1604000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1358800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1171300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1111600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1042300</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4600800</v>
+      </c>
+      <c r="E35" s="3">
         <v>3011600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1865500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1298400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2387900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2195100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1675200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>521700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1604000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1358800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1171300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1111600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1042300</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,50 +1988,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7181700</v>
+      </c>
+      <c r="E41" s="3">
         <v>4690900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3428300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3539600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4175100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3435900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2364700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1915700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2016400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1737600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1750100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1272400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2106700</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1972,107 +2061,116 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>1448100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1272000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1267500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1192700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>910100</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2198100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1919800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1575100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1197500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1306100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1314400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1127900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>862200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10182600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10089700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9831700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9200400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8237500</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2576700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2198800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1768300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1221900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1153200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1184700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>928400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>727800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>796500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>925700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>813600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>782400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>710400</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2098,23 +2196,26 @@
         <v>0</v>
       </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>245700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>290500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>308100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>331700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>249100</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2140,50 +2241,53 @@
         <v>0</v>
       </c>
       <c r="K46" s="3">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3">
         <v>14689300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14315500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13971000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12779600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12213800</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19394300</v>
+      </c>
+      <c r="E47" s="3">
         <v>15406100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>13480200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13249700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13248100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11861200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11064200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9978300</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2196,68 +2300,74 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6156500</v>
+      </c>
+      <c r="E48" s="3">
         <v>6317300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13210700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6896000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6569900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6122500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6606400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5897800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5549400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5553800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5841700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5201600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4363100</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>107400</v>
+      </c>
+      <c r="E49" s="3">
         <v>104100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>110600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>118800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>109100</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>10</v>
@@ -2268,8 +2378,8 @@
       <c r="K49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2280,9 +2390,12 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,9 +2480,12 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2392,23 +2511,26 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>871100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>749500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>912800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>646600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>595800</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40823400</v>
+      </c>
+      <c r="E54" s="3">
         <v>33275500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29509400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28260000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28361100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25482400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23440200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20638900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21109800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20618800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20725500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18627800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17172700</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,67 +2656,71 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2491900</v>
+        <v>2658100</v>
       </c>
       <c r="E57" s="3">
-        <v>6385000</v>
+        <v>2490500</v>
       </c>
       <c r="F57" s="3">
+        <v>6571900</v>
+      </c>
+      <c r="G57" s="3">
         <v>2074500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1720500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1823900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1620900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1331400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1286100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1552100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1366700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1147500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1462300</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5248500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3362100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3103200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3154100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3911800</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>10</v>
@@ -2601,60 +2734,66 @@
       <c r="L58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N58" s="3">
         <v>150000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3562700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3909900</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3850600</v>
+        <v>5140200</v>
       </c>
       <c r="E59" s="3">
-        <v>2643800</v>
+        <v>3852000</v>
       </c>
       <c r="F59" s="3">
+        <v>3081400</v>
+      </c>
+      <c r="G59" s="3">
         <v>2169400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2910900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2417000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1834400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1305900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1635100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1484000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1498800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1330300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1528800</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2680,107 +2819,116 @@
         <v>0</v>
       </c>
       <c r="K60" s="3">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3">
         <v>2921200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3036100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3015500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6040500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6901000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8988400</v>
+      </c>
+      <c r="E61" s="3">
         <v>8112100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10431800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7700200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7311900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9950500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8879400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8475200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8591500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8230600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8274200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4317400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2745500</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>698100</v>
+      </c>
+      <c r="E62" s="3">
         <v>620000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1176600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>848000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>753200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>685400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>675400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>888500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2656700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2598900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2801500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2423000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2161800</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24944600</v>
+      </c>
+      <c r="E66" s="3">
         <v>20108400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17915400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17870000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18655000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16889500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15389700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13861300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14169400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13865600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14091200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12780900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11808300</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15780300</v>
+      </c>
+      <c r="E72" s="3">
         <v>13402400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12025800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11005200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10398500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9275400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8369100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7484900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7536800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6863800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6165100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5596400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5174500</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15878800</v>
+      </c>
+      <c r="E76" s="3">
         <v>13167100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11594000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10390000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9706100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8592900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8050500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6777600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6940400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6753200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6634300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5846900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5364400</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4600800</v>
+      </c>
+      <c r="E81" s="3">
         <v>3011600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1865500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1298400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2387900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2195100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1675200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>521700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1604000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1358800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1171300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1111600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1042300</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>923900</v>
+      </c>
+      <c r="E83" s="3">
         <v>790200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>903300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1049000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1077300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1054100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1107500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>993100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>907100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>917700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>810700</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>673800</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4190000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3027000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2186700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2987200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2860300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2992300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2715800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2300800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2556000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2123600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2375700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1519000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1592600</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1262500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1390500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1632800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1638400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1970800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1952300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1846600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1964900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1725200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1537300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1872800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1803400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1647300</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2871000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2033000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1362700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1875800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2207400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1930700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1964600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1564300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1974900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1531900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2419000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,50 +4222,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1518600</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1004700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-708000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-1239800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1138600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-804300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-558300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-829300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-680500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-623800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-283100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-809500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-217400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1102200</v>
+      </c>
+      <c r="E100" s="3">
         <v>304900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-882900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1808500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>83400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>71100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-393800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-823500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-196500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-520500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>273800</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>946100</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-36300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-52400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>61600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-61500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>91600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-105800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-83700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-20800</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-53800</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2490800</v>
+      </c>
+      <c r="E102" s="3">
         <v>1262600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-111300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-635500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>739200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1071200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>449000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>278800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>477700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-834300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>65900</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>PCAR</t>
   </si>
@@ -782,16 +782,16 @@
         <v>19092400</v>
       </c>
       <c r="G9" s="3">
-        <v>15076400</v>
+        <v>15072700</v>
       </c>
       <c r="H9" s="3">
-        <v>20555100</v>
+        <v>20555600</v>
       </c>
       <c r="I9" s="3">
-        <v>18925300</v>
+        <v>18925000</v>
       </c>
       <c r="J9" s="3">
-        <v>15593400</v>
+        <v>15628900</v>
       </c>
       <c r="K9" s="3">
         <v>13517300</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8233200</v>
+        <v>6961600</v>
       </c>
       <c r="E10" s="3">
-        <v>5528700</v>
+        <v>4612200</v>
       </c>
       <c r="F10" s="3">
-        <v>4429900</v>
+        <v>3179700</v>
       </c>
       <c r="G10" s="3">
-        <v>3652100</v>
+        <v>2304700</v>
       </c>
       <c r="H10" s="3">
-        <v>5044600</v>
+        <v>3863000</v>
       </c>
       <c r="I10" s="3">
-        <v>4570400</v>
+        <v>3519500</v>
       </c>
       <c r="J10" s="3">
-        <v>3863000</v>
+        <v>2820300</v>
       </c>
       <c r="K10" s="3">
         <v>3515600</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>590700</v>
+        <v>435300</v>
       </c>
       <c r="E15" s="3">
-        <v>560800</v>
+        <v>315300</v>
       </c>
       <c r="F15" s="3">
-        <v>969400</v>
+        <v>903300</v>
       </c>
       <c r="G15" s="3">
-        <v>1008000</v>
+        <v>1049000</v>
       </c>
       <c r="H15" s="3">
-        <v>798200</v>
+        <v>1077300</v>
       </c>
       <c r="I15" s="3">
-        <v>728000</v>
+        <v>1054100</v>
       </c>
       <c r="J15" s="3">
-        <v>727500</v>
+        <v>1107500</v>
       </c>
       <c r="K15" s="3">
         <v>635200</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>29280400</v>
+        <v>29084300</v>
       </c>
       <c r="E17" s="3">
-        <v>24924800</v>
+        <v>25040500</v>
       </c>
       <c r="F17" s="3">
-        <v>21063200</v>
+        <v>21135600</v>
       </c>
       <c r="G17" s="3">
-        <v>16968500</v>
+        <v>17106600</v>
       </c>
       <c r="H17" s="3">
-        <v>22393700</v>
+        <v>22565700</v>
       </c>
       <c r="I17" s="3">
-        <v>20618900</v>
+        <v>20752500</v>
       </c>
       <c r="J17" s="3">
-        <v>17162400</v>
+        <v>17312800</v>
       </c>
       <c r="K17" s="3">
         <v>15789500</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5847000</v>
+        <v>6043100</v>
       </c>
       <c r="E18" s="3">
-        <v>3894900</v>
+        <v>3779200</v>
       </c>
       <c r="F18" s="3">
-        <v>2459100</v>
+        <v>2386700</v>
       </c>
       <c r="G18" s="3">
-        <v>1760000</v>
+        <v>1621900</v>
       </c>
       <c r="H18" s="3">
-        <v>3206000</v>
+        <v>3034000</v>
       </c>
       <c r="I18" s="3">
-        <v>2876800</v>
+        <v>2743200</v>
       </c>
       <c r="J18" s="3">
-        <v>2294000</v>
+        <v>2143600</v>
       </c>
       <c r="K18" s="3">
         <v>1243400</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>371800</v>
+        <v>-800</v>
       </c>
       <c r="E20" s="3">
-        <v>170100</v>
+        <v>-6400</v>
       </c>
       <c r="F20" s="3">
-        <v>88100</v>
+        <v>-1400</v>
       </c>
       <c r="G20" s="3">
-        <v>90000</v>
+        <v>-7900</v>
       </c>
       <c r="H20" s="3">
-        <v>133800</v>
+        <v>2900</v>
       </c>
       <c r="I20" s="3">
-        <v>135200</v>
+        <v>5300</v>
       </c>
       <c r="J20" s="3">
-        <v>-20100</v>
+        <v>3900</v>
       </c>
       <c r="K20" s="3">
         <v>42500</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7142700</v>
+        <v>6479200</v>
       </c>
       <c r="E21" s="3">
-        <v>4855200</v>
+        <v>4100900</v>
       </c>
       <c r="F21" s="3">
-        <v>3450500</v>
+        <v>3291400</v>
       </c>
       <c r="G21" s="3">
-        <v>2899000</v>
+        <v>2678800</v>
       </c>
       <c r="H21" s="3">
-        <v>4417100</v>
+        <v>4108400</v>
       </c>
       <c r="I21" s="3">
-        <v>4066100</v>
+        <v>3792000</v>
       </c>
       <c r="J21" s="3">
-        <v>3381400</v>
+        <v>3247200</v>
       </c>
       <c r="K21" s="3">
         <v>2279000</v>
@@ -1277,25 +1277,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>500600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>216300</v>
+        <v>17900</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F22" s="3">
-        <v>150900</v>
+        <v>7300</v>
       </c>
       <c r="G22" s="3">
-        <v>192100</v>
+        <v>4100</v>
       </c>
       <c r="H22" s="3">
-        <v>240600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>201800</v>
+        <v>14200</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J22" s="3">
-        <v>100600</v>
+        <v>1700</v>
       </c>
       <c r="K22" s="3">
         <v>155500</v>
@@ -1331,7 +1331,7 @@
         <v>2396300</v>
       </c>
       <c r="G23" s="3">
-        <v>1657900</v>
+        <v>1661600</v>
       </c>
       <c r="H23" s="3">
         <v>3099200</v>
@@ -1376,7 +1376,7 @@
         <v>530800</v>
       </c>
       <c r="G24" s="3">
-        <v>359500</v>
+        <v>360400</v>
       </c>
       <c r="H24" s="3">
         <v>711300</v>
@@ -1385,7 +1385,7 @@
         <v>615100</v>
       </c>
       <c r="J24" s="3">
-        <v>671500</v>
+        <v>498100</v>
       </c>
       <c r="K24" s="3">
         <v>608700</v>
@@ -1466,7 +1466,7 @@
         <v>1865500</v>
       </c>
       <c r="G26" s="3">
-        <v>1298400</v>
+        <v>1301200</v>
       </c>
       <c r="H26" s="3">
         <v>2387900</v>
@@ -1475,7 +1475,7 @@
         <v>2195100</v>
       </c>
       <c r="J26" s="3">
-        <v>1501800</v>
+        <v>1675200</v>
       </c>
       <c r="K26" s="3">
         <v>521700</v>
@@ -1511,7 +1511,7 @@
         <v>1865500</v>
       </c>
       <c r="G27" s="3">
-        <v>1298400</v>
+        <v>1301200</v>
       </c>
       <c r="H27" s="3">
         <v>2387900</v>
@@ -1520,7 +1520,7 @@
         <v>2195100</v>
       </c>
       <c r="J27" s="3">
-        <v>1501800</v>
+        <v>1675200</v>
       </c>
       <c r="K27" s="3">
         <v>521700</v>
@@ -1591,26 +1591,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>10</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>173400</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>10</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-371800</v>
+        <v>800</v>
       </c>
       <c r="E32" s="3">
-        <v>-170100</v>
+        <v>6400</v>
       </c>
       <c r="F32" s="3">
-        <v>-88100</v>
+        <v>1400</v>
       </c>
       <c r="G32" s="3">
-        <v>-90000</v>
+        <v>7900</v>
       </c>
       <c r="H32" s="3">
-        <v>-133800</v>
+        <v>-2900</v>
       </c>
       <c r="I32" s="3">
-        <v>-135200</v>
+        <v>-5300</v>
       </c>
       <c r="J32" s="3">
-        <v>20100</v>
+        <v>-3900</v>
       </c>
       <c r="K32" s="3">
         <v>-42500</v>
@@ -1781,7 +1781,7 @@
         <v>1865500</v>
       </c>
       <c r="G33" s="3">
-        <v>1298400</v>
+        <v>1301200</v>
       </c>
       <c r="H33" s="3">
         <v>2387900</v>
@@ -1871,7 +1871,7 @@
         <v>1865500</v>
       </c>
       <c r="G35" s="3">
-        <v>1298400</v>
+        <v>1301200</v>
       </c>
       <c r="H35" s="3">
         <v>2387900</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7181700</v>
+        <v>6836700</v>
       </c>
       <c r="E41" s="3">
-        <v>4690900</v>
+        <v>4544700</v>
       </c>
       <c r="F41" s="3">
-        <v>3428300</v>
+        <v>3253600</v>
       </c>
       <c r="G41" s="3">
-        <v>3539600</v>
+        <v>3405000</v>
       </c>
       <c r="H41" s="3">
-        <v>4175100</v>
+        <v>4007300</v>
       </c>
       <c r="I41" s="3">
-        <v>3435900</v>
+        <v>3279200</v>
       </c>
       <c r="J41" s="3">
-        <v>2364700</v>
+        <v>2254800</v>
       </c>
       <c r="K41" s="3">
         <v>1915700</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1822600</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1614200</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1559400</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>1429000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1162100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>1020400</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1367100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2136,7 +2136,7 @@
         <v>2198800</v>
       </c>
       <c r="F44" s="3">
-        <v>1768300</v>
+        <v>1976000</v>
       </c>
       <c r="G44" s="3">
         <v>1221900</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>680600</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>682000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>732900</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>515600</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>388000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>364700</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>404400</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>32388900</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>25106500</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>21320200</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>20134900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>20733300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>18483500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>16177800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2264,26 +2264,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>19394300</v>
-      </c>
-      <c r="E47" s="3">
-        <v>15406100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>13480200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>13249700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>13248100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>11861200</v>
-      </c>
-      <c r="J47" s="3">
-        <v>11064200</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K47" s="3">
         <v>9978300</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6156500</v>
+        <v>3975100</v>
       </c>
       <c r="E48" s="3">
-        <v>6317300</v>
+        <v>3698800</v>
       </c>
       <c r="F48" s="3">
-        <v>13210700</v>
+        <v>3731200</v>
       </c>
       <c r="G48" s="3">
-        <v>6896000</v>
+        <v>3724200</v>
       </c>
       <c r="H48" s="3">
-        <v>6569900</v>
+        <v>3462100</v>
       </c>
       <c r="I48" s="3">
-        <v>6122500</v>
+        <v>3267500</v>
       </c>
       <c r="J48" s="3">
-        <v>6606400</v>
+        <v>3730100</v>
       </c>
       <c r="K48" s="3">
         <v>5897800</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>107400</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>104100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>110600</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>118800</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>109100</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>10</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>1267100</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>1238600</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>1210800</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>876600</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>695500</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>554800</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>354200</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2658100</v>
+        <v>1667600</v>
       </c>
       <c r="E57" s="3">
-        <v>2490500</v>
+        <v>1665100</v>
       </c>
       <c r="F57" s="3">
-        <v>6571900</v>
+        <v>1393500</v>
       </c>
       <c r="G57" s="3">
-        <v>2074500</v>
+        <v>1176200</v>
       </c>
       <c r="H57" s="3">
-        <v>1720500</v>
+        <v>1115700</v>
       </c>
       <c r="I57" s="3">
-        <v>1823900</v>
+        <v>1304900</v>
       </c>
       <c r="J57" s="3">
-        <v>1620900</v>
+        <v>1154700</v>
       </c>
       <c r="K57" s="3">
         <v>1331400</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5248500</v>
+        <v>7581200</v>
       </c>
       <c r="E58" s="3">
-        <v>3362100</v>
+        <v>3361600</v>
       </c>
       <c r="F58" s="3">
-        <v>3103200</v>
+        <v>3094200</v>
       </c>
       <c r="G58" s="3">
-        <v>3154100</v>
+        <v>3243500</v>
       </c>
       <c r="H58" s="3">
-        <v>3911800</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>10</v>
+        <v>3843400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3275300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>2822000</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>10</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5140200</v>
+        <v>4949200</v>
       </c>
       <c r="E59" s="3">
-        <v>3852000</v>
+        <v>3436200</v>
       </c>
       <c r="F59" s="3">
-        <v>3081400</v>
+        <v>2252200</v>
       </c>
       <c r="G59" s="3">
-        <v>2169400</v>
+        <v>1905200</v>
       </c>
       <c r="H59" s="3">
-        <v>2910900</v>
+        <v>2291500</v>
       </c>
       <c r="I59" s="3">
-        <v>2417000</v>
+        <v>1670900</v>
       </c>
       <c r="J59" s="3">
-        <v>1834400</v>
+        <v>1319400</v>
       </c>
       <c r="K59" s="3">
         <v>1305900</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>16530200</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>10453700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>8285100</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>7595800</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>8619600</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>7669500</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>6404800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8988400</v>
+        <v>57100</v>
       </c>
       <c r="E61" s="3">
-        <v>8112100</v>
+        <v>32000</v>
       </c>
       <c r="F61" s="3">
-        <v>10431800</v>
+        <v>22300</v>
       </c>
       <c r="G61" s="3">
-        <v>7700200</v>
+        <v>27400</v>
       </c>
       <c r="H61" s="3">
-        <v>7311900</v>
+        <v>23700</v>
       </c>
       <c r="I61" s="3">
-        <v>9950500</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>8879400</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>8475200</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>698100</v>
+        <v>787600</v>
       </c>
       <c r="E62" s="3">
-        <v>620000</v>
+        <v>657000</v>
       </c>
       <c r="F62" s="3">
-        <v>1176600</v>
+        <v>993000</v>
       </c>
       <c r="G62" s="3">
-        <v>848000</v>
+        <v>1164100</v>
       </c>
       <c r="H62" s="3">
-        <v>753200</v>
+        <v>1132400</v>
       </c>
       <c r="I62" s="3">
-        <v>685400</v>
+        <v>1118300</v>
       </c>
       <c r="J62" s="3">
-        <v>675400</v>
+        <v>1283900</v>
       </c>
       <c r="K62" s="3">
         <v>888500</v>
@@ -3641,7 +3641,7 @@
         <v>1865500</v>
       </c>
       <c r="G81" s="3">
-        <v>1298400</v>
+        <v>1301200</v>
       </c>
       <c r="H81" s="3">
         <v>2387900</v>
@@ -3696,10 +3696,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>923900</v>
+        <v>435300</v>
       </c>
       <c r="E83" s="3">
-        <v>790200</v>
+        <v>315300</v>
       </c>
       <c r="F83" s="3">
         <v>903300</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1518600</v>
+        <v>1518600</v>
       </c>
       <c r="E96" s="3">
-        <v>-1004700</v>
+        <v>1004700</v>
       </c>
       <c r="F96" s="3">
-        <v>-708000</v>
+        <v>708000</v>
       </c>
       <c r="G96" s="3">
-        <v>-1239800</v>
+        <v>1239800</v>
       </c>
       <c r="H96" s="3">
-        <v>-1138600</v>
+        <v>435800</v>
       </c>
       <c r="I96" s="3">
-        <v>-804300</v>
+        <v>804300</v>
       </c>
       <c r="J96" s="3">
-        <v>-558300</v>
+        <v>287300</v>
       </c>
       <c r="K96" s="3">
         <v>-829300</v>

--- a/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>PCAR</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>33663800</v>
+      </c>
+      <c r="E8" s="3">
         <v>35127400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28819700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23522300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>18728500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25599700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23495700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19456400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17032900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19115100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18997000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17123800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17050500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16355200</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>26069600</v>
+      </c>
+      <c r="E9" s="3">
         <v>26894200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>23291000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19092400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15072700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20555600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18925000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15628900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13517300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15292800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15486900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13902000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27975300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13523100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5930300</v>
+      </c>
+      <c r="E10" s="3">
         <v>6961600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4612200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3179700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2304700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3863000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3519500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2820300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3515600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3822300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3510100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3221800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-10924800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2832100</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,53 +888,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>452900</v>
+      </c>
+      <c r="E12" s="3">
         <v>410900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>341200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>324100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>273900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>326600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>306100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>264700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>247200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>239800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>215600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>251400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>279300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>288200</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -965,17 +981,20 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E14" s="3">
         <v>600000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -992,11 +1011,11 @@
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3">
         <v>833000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
@@ -1010,54 +1029,60 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>372200</v>
+      </c>
+      <c r="E15" s="3">
         <v>435300</v>
       </c>
-      <c r="E15" s="3">
-        <v>315300</v>
-      </c>
       <c r="F15" s="3">
+        <v>790200</v>
+      </c>
+      <c r="G15" s="3">
         <v>903300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1049000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1077300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1054100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1107500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>635200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>583700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>588500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>571700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>517400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>346600</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28671300</v>
+      </c>
+      <c r="E17" s="3">
         <v>29084300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25040500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21135600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17106600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22565700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20752500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17312800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15789500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16672500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16862600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15297500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15296900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14875800</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4992500</v>
+      </c>
+      <c r="E18" s="3">
         <v>6043100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3779200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2386700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1621900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3034000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2743200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2143600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1243400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2442600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2134400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1826300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1753600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1479400</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>42500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>20100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>35700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>33100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>27500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5399700</v>
+      </c>
+      <c r="E21" s="3">
         <v>6479200</v>
       </c>
-      <c r="E21" s="3">
-        <v>4100900</v>
-      </c>
       <c r="F21" s="3">
+        <v>4575800</v>
+      </c>
+      <c r="G21" s="3">
         <v>3291400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2678800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4108400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3792000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3247200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2279000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3369800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3064800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2672700</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2180700</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E22" s="3">
         <v>17900</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14200</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>155500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>125600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>129500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>167000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>157800</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5400900</v>
+      </c>
+      <c r="E23" s="3">
         <v>5718200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3848700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2396300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1661600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3099200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2810200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2173300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1130400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2337100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2017600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1695000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1628900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1506900</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1238900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1117400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>837100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>530800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>360400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>711300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>615100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>498100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>608700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>733100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>658800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>523700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>517300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>464600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4162000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4600800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3011600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1865500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1301200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2387900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2195100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1675200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>521700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1604000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1358800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1171300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1111600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1042300</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4162000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4600800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3011600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1865500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1301200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2387900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2195100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1675200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>521700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1604000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1358800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1171300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1111600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1042300</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1612,8 +1672,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>10</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>10</v>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-42500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-20100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-35700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-33100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-27500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4162000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4600800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3011600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1865500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1301200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2387900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2195100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1675200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>521700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1604000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1358800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1171300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1111600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1042300</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4162000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4600800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3011600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1865500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1301200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2387900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2195100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1675200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>521700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1604000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1358800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1171300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1111600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1042300</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,278 +2074,297 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6871100</v>
+      </c>
+      <c r="E41" s="3">
         <v>6836700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4544700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3253600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3405000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4007300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3279200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2254800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1915700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2016400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1737600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1750100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1272400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2106700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2778800</v>
+      </c>
+      <c r="E42" s="3">
         <v>1822600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1614200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1559400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1429000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1162100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1020400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1367100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>1448100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1272000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1267500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1192700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>910100</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1933800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2198100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1919800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1575100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1197500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1306100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1314400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1127900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>862200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10182600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10089700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9831700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9200400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8237500</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2367100</v>
+      </c>
+      <c r="E44" s="3">
         <v>2576700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2198800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1976000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1221900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1153200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1184700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>928400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>727800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>796500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>925700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>813600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>782400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>710400</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>751200</v>
+      </c>
+      <c r="E45" s="3">
         <v>680600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>682000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>732900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>515600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>388000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>364700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>404400</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>245700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>290500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>308100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>331700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>249100</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34821600</v>
+      </c>
+      <c r="E46" s="3">
         <v>32388900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25106500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21320200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20134900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20733300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18483500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16177800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3">
         <v>14689300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14315500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13971000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12779600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12213800</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2285,12 +2389,12 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="3">
         <v>9978300</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2303,54 +2407,60 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4122100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3975100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3698800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3731200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3724200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3462100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3267500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3730100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5897800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5549400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5553800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5841700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5201600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4363100</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2375,14 +2485,14 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>10</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2393,9 +2503,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1698100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1267100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1238600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1210800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>876600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>695500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>554800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>354200</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>871100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>749500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>912800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>646600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>595800</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43418900</v>
+      </c>
+      <c r="E54" s="3">
         <v>40823400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33275500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29509400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28260000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28361100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25482400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23440200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20638900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21109800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20618800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20725500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18627800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17172700</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,79 +2786,83 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1598700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1667600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1665100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1393500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1176200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1115700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1304900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1154700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1331400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1286100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1552100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1366700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1147500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1462300</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7581200</v>
+        <v>8407200</v>
       </c>
       <c r="E58" s="3">
+        <v>5216800</v>
+      </c>
+      <c r="F58" s="3">
         <v>3361600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3094200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3243500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3843400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3275300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2822000</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>10</v>
@@ -2737,198 +2870,213 @@
       <c r="M58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O58" s="3">
         <v>150000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3562700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3909900</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4949200</v>
+        <v>4653800</v>
       </c>
       <c r="E59" s="3">
+        <v>4845500</v>
+      </c>
+      <c r="F59" s="3">
         <v>3436200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2252200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1905200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2291500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1670900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1319400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1305900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1635100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1484000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1498800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1330300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1528800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>16530200</v>
+        <v>17078200</v>
       </c>
       <c r="E60" s="3">
+        <v>14062100</v>
+      </c>
+      <c r="F60" s="3">
         <v>10453700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8285100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7595800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8619600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7669500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6404800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
         <v>2921200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3036100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3015500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6040500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6901000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E61" s="3">
         <v>57100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>32000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23700</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>8475200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8591500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8230600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8274200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4317400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2745500</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>787600</v>
+        <v>470800</v>
       </c>
       <c r="E62" s="3">
+        <v>874600</v>
+      </c>
+      <c r="F62" s="3">
         <v>657000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>993000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1164100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1132400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1118300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1283900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>888500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2656700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2598900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2801500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2423000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2161800</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25912000</v>
+      </c>
+      <c r="E66" s="3">
         <v>24944600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20108400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17915400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17870000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18655000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16889500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15389700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13861300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14169400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13865600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14091200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12780900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11808300</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17751000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15780300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13402400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12025800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11005200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10398500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9275400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8369100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7484900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7536800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6863800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6165100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5596400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5174500</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17506900</v>
+      </c>
+      <c r="E76" s="3">
         <v>15878800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13167100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11594000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10390000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9706100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8592900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8050500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6777600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6940400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6753200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6634300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5846900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5364400</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4162000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4600800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3011600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1865500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1301200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2387900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2195100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1675200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>521700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1604000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1358800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1171300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1111600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1042300</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>372200</v>
+      </c>
+      <c r="E83" s="3">
         <v>435300</v>
       </c>
-      <c r="E83" s="3">
-        <v>315300</v>
-      </c>
       <c r="F83" s="3">
+        <v>790200</v>
+      </c>
+      <c r="G83" s="3">
         <v>903300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1049000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1077300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1054100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1107500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>993100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>907100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>917700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>810700</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>673800</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4640900</v>
+      </c>
+      <c r="E89" s="3">
         <v>4190000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3027000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2186700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2987200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2860300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2992300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2715800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2300800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2556000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2123600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2375700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1519000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1592600</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1745600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1262500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1390500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1632800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1638400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1970800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1952300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1846600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1964900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1725200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1537300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1872800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1803400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1647300</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4487300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2871000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2033000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1362700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1875800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2207400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1930700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1964600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1564300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1974900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1531900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2419000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2288500</v>
+      </c>
+      <c r="E96" s="3">
         <v>1518600</v>
       </c>
-      <c r="E96" s="3">
-        <v>1004700</v>
-      </c>
       <c r="F96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G96" s="3">
         <v>708000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1239800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>435800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>804300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>287300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-829300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-680500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-623800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-283100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-809500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-217400</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-123100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1102200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>304900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-882900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1808500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>83400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>71100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-393800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-823500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-196500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-520500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>273800</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>946100</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-151400</v>
+      </c>
+      <c r="E101" s="3">
         <v>69600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-36300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-52400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>61600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-61500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>91600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-13700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-105800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-83700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-20800</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-53800</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-120900</v>
+      </c>
+      <c r="E102" s="3">
         <v>2490800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1262600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-111300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-635500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>739200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1071200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>449000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>278800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>477700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-834300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>65900</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>PCAR</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28444800</v>
+      </c>
+      <c r="E8" s="3">
         <v>33663800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35127400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28819700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23522300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18728500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>25599700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23495700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19456400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17032900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19115100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18997000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17123800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17050500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16355200</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>22736700</v>
+      </c>
+      <c r="E9" s="3">
         <v>26069600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26894200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>23291000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19092400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15072700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>20555600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18925000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15628900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13517300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15292800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15486900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13902000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27975300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13523100</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3983800</v>
+      </c>
+      <c r="E10" s="3">
         <v>5930300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6961600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4612200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3179700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2304700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3863000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3519500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2820300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3515600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3822300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3510100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3221800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-10924800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2832100</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,56 +901,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>445500</v>
+      </c>
+      <c r="E12" s="3">
         <v>452900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>410900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>341200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>324100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>273900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>326600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>306100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>264700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>247200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>239800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>215600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>251400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>279300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>288200</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -984,20 +1000,23 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>352000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-14000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>600000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -1014,11 +1033,11 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3">
         <v>833000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
@@ -1032,57 +1051,63 @@
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>357400</v>
+      </c>
+      <c r="E15" s="3">
         <v>372200</v>
       </c>
-      <c r="E15" s="3">
-        <v>435300</v>
-      </c>
       <c r="F15" s="3">
+        <v>923900</v>
+      </c>
+      <c r="G15" s="3">
         <v>790200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>903300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1049000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1077300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1054100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1107500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>635200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>583700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>588500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>571700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>517400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>346600</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25379200</v>
+      </c>
+      <c r="E17" s="3">
         <v>28671300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29084300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25040500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21135600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17106600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22565700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20752500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17312800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15789500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16672500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16862600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15297500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15296900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14875800</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3065600</v>
+      </c>
+      <c r="E18" s="3">
         <v>4992500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6043100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3779200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2386700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1621900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3034000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2743200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2143600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1243400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2442600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2134400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1826300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1753600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1479400</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-35000</v>
+        <v>38800</v>
       </c>
       <c r="E20" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>42500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>20100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>35700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>33100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>27500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5399700</v>
+        <v>3384200</v>
       </c>
       <c r="E21" s="3">
-        <v>6479200</v>
+        <v>5400300</v>
       </c>
       <c r="F21" s="3">
+        <v>6967800</v>
+      </c>
+      <c r="G21" s="3">
         <v>4575800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3291400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2678800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4108400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3792000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3247200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2279000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3369800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3064800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2672700</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2180700</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>35300</v>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E22" s="3">
+        <v>35900</v>
+      </c>
+      <c r="F22" s="3">
         <v>17900</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14200</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>155500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>125600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>129500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>167000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>157800</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3023500</v>
+      </c>
+      <c r="E23" s="3">
         <v>5400900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5718200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3848700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2396300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1661600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3099200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2810200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2173300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1130400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2337100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2017600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1695000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1628900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1506900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>647700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1238900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1117400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>837100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>530800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>360400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>711300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>615100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>498100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>608700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>733100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>658800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>523700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>517300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>464600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2375800</v>
+      </c>
+      <c r="E26" s="3">
         <v>4162000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4600800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3011600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1865500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1301200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2387900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2195100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1675200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>521700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1604000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1358800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1171300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1111600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1042300</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2375800</v>
+      </c>
+      <c r="E27" s="3">
         <v>4162000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4600800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3011600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1865500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1301200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2387900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2195100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1675200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>521700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1604000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1358800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1171300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1111600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1042300</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,8 +1735,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>10</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>10</v>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>35000</v>
+        <v>-38800</v>
       </c>
       <c r="E32" s="3">
+        <v>35600</v>
+      </c>
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-42500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-20100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-35700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-27500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2375800</v>
+      </c>
+      <c r="E33" s="3">
         <v>4162000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4600800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3011600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1865500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1301200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2387900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2195100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1675200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>521700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1604000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1358800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1171300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1111600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1042300</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2375800</v>
+      </c>
+      <c r="E35" s="3">
         <v>4162000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4600800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3011600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1865500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1301200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2387900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2195100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1675200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>521700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1604000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1358800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1171300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1111600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1042300</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,296 +2160,315 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6046000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6871100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6836700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4544700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3253600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3405000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4007300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3279200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2254800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1915700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2016400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1737600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1750100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1272400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2106700</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3207700</v>
+      </c>
+      <c r="E42" s="3">
         <v>2778800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1822600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1614200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1559400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1429000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1162100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1020400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1367100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>1448100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1272000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1267500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1192700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>910100</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1981100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1933800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2198100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1919800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1575100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1197500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1306100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1314400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1127900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>862200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10182600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10089700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9831700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9200400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8237500</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2187500</v>
+      </c>
+      <c r="E44" s="3">
         <v>2367100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2576700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2198800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1976000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1221900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1153200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1184700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>928400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>727800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>796500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>925700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>813600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>782400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>710400</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>903900</v>
+      </c>
+      <c r="E45" s="3">
         <v>751200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>680600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>682000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>732900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>515600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>388000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>364700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>404400</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>245700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>290500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>308100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>331700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>249100</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34876200</v>
+      </c>
+      <c r="E46" s="3">
         <v>34821600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32388900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25106500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21320200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20134900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20733300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18483500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16177800</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3">
         <v>14689300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14315500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13971000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12779600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12213800</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2392,12 +2496,12 @@
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M47" s="3">
         <v>9978300</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -2410,57 +2514,63 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4621700</v>
+      </c>
+      <c r="E48" s="3">
         <v>4122100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3975100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3698800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3731200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3724200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3462100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3267500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3730100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5897800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5549400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5553800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5841700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5201600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4363100</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2488,14 +2598,14 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>10</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2506,9 +2616,12 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2354900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1698100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1267100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1238600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1210800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>876600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>695500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>554800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>354200</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>871100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>749500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>912800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>646600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>595800</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44336200</v>
+      </c>
+      <c r="E54" s="3">
         <v>43418900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>40823400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33275500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29509400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28260000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28361100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25482400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23440200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20638900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21109800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20618800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20725500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18627800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17172700</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,85 +2916,89 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1598700</v>
+        <v>2349700</v>
       </c>
       <c r="E57" s="3">
+        <v>2699500</v>
+      </c>
+      <c r="F57" s="3">
         <v>1667600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1665100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1393500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1176200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1115700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1304900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1154700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1331400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1286100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1552100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1366700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1147500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1462300</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8407200</v>
+        <v>8387400</v>
       </c>
       <c r="E58" s="3">
+        <v>5544700</v>
+      </c>
+      <c r="F58" s="3">
         <v>5216800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3361600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3094200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3243500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3843400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3275300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2822000</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>10</v>
@@ -2873,210 +3006,225 @@
       <c r="N58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P58" s="3">
         <v>150000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3562700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3909900</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4653800</v>
+        <v>3905200</v>
       </c>
       <c r="E59" s="3">
+        <v>4603300</v>
+      </c>
+      <c r="F59" s="3">
         <v>4845500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3436200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2252200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1905200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2291500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1670900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1319400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1305900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1635100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1484000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1498800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1330300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1528800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>17078200</v>
+        <v>16083800</v>
       </c>
       <c r="E60" s="3">
+        <v>14165200</v>
+      </c>
+      <c r="F60" s="3">
         <v>14062100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10453700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8285100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7595800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8619600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7669500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6404800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3">
         <v>2921200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3036100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3015500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6040500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6901000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E61" s="3">
         <v>54400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>32000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23700</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>8475200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8591500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8230600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8274200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4317400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2745500</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>470800</v>
+        <v>733300</v>
       </c>
       <c r="E62" s="3">
+        <v>512300</v>
+      </c>
+      <c r="F62" s="3">
         <v>874600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>657000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>993000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1164100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1132400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1118300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1283900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>888500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2656700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2598900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2801500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2423000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2161800</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25072200</v>
+      </c>
+      <c r="E66" s="3">
         <v>25912000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24944600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20108400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17915400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17870000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18655000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16889500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15389700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13861300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14169400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13865600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14091200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12780900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11808300</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18696100</v>
+      </c>
+      <c r="E72" s="3">
         <v>17751000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15780300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13402400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12025800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11005200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10398500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9275400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8369100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7484900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7536800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6863800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6165100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5596400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5174500</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19264000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17506900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15878800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13167100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11594000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10390000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9706100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8592900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8050500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6777600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6940400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6753200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6634300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5846900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5364400</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2375800</v>
+      </c>
+      <c r="E81" s="3">
         <v>4162000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4600800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3011600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1865500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1301200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2387900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2195100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1675200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>521700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1604000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1358800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1171300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1111600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1042300</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>357400</v>
+      </c>
+      <c r="E83" s="3">
         <v>372200</v>
       </c>
-      <c r="E83" s="3">
-        <v>435300</v>
-      </c>
       <c r="F83" s="3">
+        <v>923900</v>
+      </c>
+      <c r="G83" s="3">
         <v>790200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>903300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1049000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1077300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1054100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1107500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>993100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>907100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>917700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>810700</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>673800</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4415800</v>
+      </c>
+      <c r="E89" s="3">
         <v>4640900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4190000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3027000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2186700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2987200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2860300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2992300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2715800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2300800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2556000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2123600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2375700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1519000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1592600</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1386600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1745600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1262500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1390500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1632800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1638400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1970800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1952300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1846600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1964900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1725200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1537300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1872800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1803400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1647300</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2267200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4487300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2871000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2033000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1362700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1875800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2207400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1930700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1964600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1564300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1974900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1531900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2151000</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2419000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2267100</v>
+      </c>
+      <c r="E96" s="3">
         <v>2288500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1518600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>708000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1239800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>435800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>804300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>287300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-829300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-680500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-623800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-283100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-809500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-217400</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3082400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-123100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1102200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>304900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-882900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1808500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>83400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>71100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-393800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-823500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-196500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-520500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>273800</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>946100</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>180900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-151400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>69600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-36300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-52400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>61600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-61500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>91600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-105800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-83700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-20800</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-53800</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-752900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-120900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2490800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1262600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-111300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-635500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>739200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1071200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>449000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-100700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>278800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>477700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-834300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>65900</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
